--- a/docs/test/unit/NOUS-103/観点表_memoryUpdater.xlsx
+++ b/docs/test/unit/NOUS-103/観点表_memoryUpdater.xlsx
@@ -13,9 +13,9 @@
     <sheet name="対象概要" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'観点表'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>TC-UT_MEM-014</t>
+          <t>TC-UT_MEM-015</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>clip</t>
+          <t>updateMemories</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2019,40 +2019,40 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>境界値</t>
+          <t>同値分割</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>clip はちょうど n 字ならそのまま、n＋1 字なら n 字に切る</t>
+          <t>起点の本文は sanitizeTimelineText を通してから conversation_summary に入れる</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>前提：なし
-入力：clip(あいう, 3)、clip(あいうえ, 3)</t>
+          <t>前提：haruka の起点（本文に &lt;/timeline&gt; を含む）
+入力：minato が起点に返信</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>あいう、あいう</t>
+          <t>conversation_summary の起点の本文は ＜/timeline＞ に置き換わり、&lt;/timeline&gt; を含まない</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>B3-T, B3-F</t>
+          <t>B10-T</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>一時 DB（createTestDb、マイグレーション済み）。generationSeed で世界・エージェント・生成イベントを入れる</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr"/>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_MEM-014 clip はちょうど n 字ならそのまま、n＋1 字なら n 字に切る</t>
+          <t>TC-UT_MEM-015 起点の本文は sanitizeTimelineText を通してから conversation_summary に入れる</t>
         </is>
       </c>
       <c r="N24" s="6" t="inlineStr">
@@ -2064,13 +2064,85 @@
       <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
+          <t>既存テスト：なし
+疑い：疑い 2：起点の本文を sanitizeTimelineText に通さずに入れている
+2026-10-26 Kouhei Tajima さんの決定（NOUS-103）：記憶に入れる前に起点の本文に sanitizeTimelineText を通す</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>TC-UT_MEM-014</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>clip</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>境界値</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>clip はちょうど n 字ならそのまま、n＋1 字なら n 字に切る</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>前提：なし
+入力：clip(あいう, 3)、clip(あいうえ, 3)</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>あいう、あいう</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>B3-T, B3-F</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>TC-UT_MEM-014 clip はちょうど n 字ならそのまま、n＋1 字なら n 字に切る</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
           <t>既存テスト：一部 TC-NOUS62_DEV-36（n より短い・長い場合）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q24"/>
-  <conditionalFormatting sqref="A5:Q74">
+  <autoFilter ref="A4:Q25"/>
+  <conditionalFormatting sqref="A5:Q75">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$N5="NG"</formula>
     </cfRule>
@@ -2082,10 +2154,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N5:N74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,OK,NG,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"正常系,異常系"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2137,7 +2209,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTA(観点表!$B$5:$B$74)</f>
+        <f>COUNTA(観点表!$B$5:$B$75)</f>
         <v/>
       </c>
     </row>
@@ -2148,7 +2220,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$74,"正常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$75,"正常系")</f>
         <v/>
       </c>
     </row>
@@ -2159,7 +2231,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$74,"異常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$75,"異常系")</f>
         <v/>
       </c>
     </row>
@@ -2179,7 +2251,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$74,"分岐網羅")</f>
+        <f>COUNTIF(観点表!$E$5:$E$75,"分岐網羅")</f>
         <v/>
       </c>
     </row>
@@ -2190,7 +2262,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$74,"同値分割")</f>
+        <f>COUNTIF(観点表!$E$5:$E$75,"同値分割")</f>
         <v/>
       </c>
     </row>
@@ -2201,7 +2273,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$74,"境界値")</f>
+        <f>COUNTIF(観点表!$E$5:$E$75,"境界値")</f>
         <v/>
       </c>
     </row>
@@ -2212,7 +2284,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$74,"開発者テスト")</f>
+        <f>COUNTIF(観点表!$E$5:$E$75,"開発者テスト")</f>
         <v/>
       </c>
     </row>
@@ -2232,7 +2304,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>COUNTIF(観点表!$K$5:$K$74,"?*")</f>
+        <f>COUNTIF(観点表!$K$5:$K$75,"?*")</f>
         <v/>
       </c>
     </row>
@@ -2263,7 +2335,7 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$74,"未実施")</f>
+        <f>COUNTIF(観点表!$N$5:$N$75,"未実施")</f>
         <v/>
       </c>
     </row>
@@ -2274,7 +2346,7 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$74,"OK")</f>
+        <f>COUNTIF(観点表!$N$5:$N$75,"OK")</f>
         <v/>
       </c>
     </row>
@@ -2285,7 +2357,7 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$74,"NG")</f>
+        <f>COUNTIF(観点表!$N$5:$N$75,"NG")</f>
         <v/>
       </c>
     </row>
@@ -2296,7 +2368,7 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$74,"保留")</f>
+        <f>COUNTIF(観点表!$N$5:$N$75,"保留")</f>
         <v/>
       </c>
     </row>
@@ -2307,7 +2379,7 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$74,"対象外")</f>
+        <f>COUNTIF(観点表!$N$5:$N$75,"対象外")</f>
         <v/>
       </c>
     </row>
@@ -2344,7 +2416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2784,12 +2856,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>TC-UT_MEM-014</t>
+          <t>TC-UT_MEM-015</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>clip はちょうど n 字ならそのまま、n＋1 字なら n 字に切る</t>
+          <t>起点の本文は sanitizeTimelineText を通してから conversation_summary に入れる</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -2801,8 +2873,28 @@
       <c r="E24" s="13" t="inlineStr"/>
       <c r="F24" s="13" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>TC-UT_MEM-014</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>clip はちょうど n 字ならそのまま、n＋1 字なら n 字に切る</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr"/>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F24"/>
+  <autoFilter ref="A4:F25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3105,14 +3197,14 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 1：conversation_summary には他の住人の投稿（起点）の先頭 40 字が入り、記憶は system に入る。11章（NFR-S-012）の「他の住人の投稿は user の &lt;timeline&gt; の中だけに置く」と、8章の conversation_summary の内容が両立していない。NOUS-102 の確認事項（promptBuilder）と同じ件。</t>
+          <t>・疑い 2：conversation_summary に入れる起点の本文（他の住人の投稿の先頭 40 字）を sanitizeTimelineText に通していない（TC-UT_MEM-015）。2026-10-26 に Kouhei Tajima さんが、記憶に入れる前に sanitizeTimelineText を通すことを仕様と決めた（NFR-S-012。NOUS-102 の確認事項と同じ件）。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 2：relationship_summary の同数のときの並び（フォロー中が先、次にハンドルの順）は設計書に記載がなく、実装の値を期待値にした（TC-UT_MEM-006）。</t>
+          <t>・確認事項 1：relationship_summary の同数のときの並び（フォロー中が先、次にハンドルの順）は設計書に記載がなく、実装の値を期待値にした（TC-UT_MEM-006）。</t>
         </is>
       </c>
     </row>
